--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Table1_AE_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Table1_AE_Raw.xlsx
@@ -413,12 +413,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X-ray</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17813 (22.26%)</t>
+          <t>19199 (21.16%)</t>
         </is>
       </c>
     </row>
@@ -430,12 +430,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Haematology</t>
+          <t>X-ray</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10987 (13.73%)</t>
+          <t>17813 (19.63%)</t>
         </is>
       </c>
     </row>
@@ -447,12 +447,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Haematology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10925 (13.65%)</t>
+          <t>10987 (12.11%)</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8492 (10.61%)</t>
+          <t>10925 (12.04%)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7591 (9.49%)</t>
+          <t>7591 (8.37%)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6602 (8.25%)</t>
+          <t>6602 (7.28%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3791 (4.74%)</t>
+          <t>3791 (4.18%)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2313 (2.89%)</t>
+          <t>2313 (2.55%)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2163 (2.7%)</t>
+          <t>2163 (2.38%)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2021 (2.53%)</t>
+          <t>2021 (2.23%)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1958 (2.45%)</t>
+          <t>1958 (2.16%)</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1736 (2.15%)</t>
+          <t>1736 (1.91%)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1443 (1.8%)</t>
+          <t>1443 (1.59%)</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1205 (1.51%)</t>
+          <t>1205 (1.33%)</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>977 (1.22%)</t>
+          <t>977 (1.08%)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>27594 (35.7%)</t>
+          <t>30916 (38.35%)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7201 (9.32%)</t>
+          <t>7201 (8.93%)</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6048 (7.82%)</t>
+          <t>6048 (7.5%)</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5179 (6.7%)</t>
+          <t>5179 (6.42%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4878 (6.28%)</t>
+          <t>4878 (6.02%)</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3950 (5.11%)</t>
+          <t>3950 (4.9%)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3870 (5.01%)</t>
+          <t>3870 (4.8%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3189 (4.13%)</t>
+          <t>3189 (3.96%)</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2965 (3.84%)</t>
+          <t>2965 (3.68%)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2724 (3.52%)</t>
+          <t>2724 (3.38%)</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2014 (2.61%)</t>
+          <t>2014 (2.5%)</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1669 (2.16%)</t>
+          <t>1669 (2.07%)</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1593 (2.06%)</t>
+          <t>1593 (1.98%)</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1512 (1.96%)</t>
+          <t>1512 (1.88%)</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1140 (1.47%)</t>
+          <t>1140 (1.41%)</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>919 (1.19%)</t>
+          <t>919 (1.14%)</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>856 (1.11%)</t>
+          <t>856 (1.06%)</t>
         </is>
       </c>
     </row>
